--- a/edtech-news-tracker/edtech_tracking_list.xlsx
+++ b/edtech-news-tracker/edtech_tracking_list.xlsx
@@ -425,13 +425,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +456,11 @@
           <t>HQ Country</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -462,9 +468,11 @@
           <t>ABA English</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -472,9 +480,6 @@
           <t>ABC Pathways School</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -482,9 +487,6 @@
           <t>ABT Global</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -492,9 +494,6 @@
           <t>AMIDEAST</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -502,9 +501,6 @@
           <t>Abdulla Al Ghurair Foundation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -512,9 +508,16 @@
           <t>Acadomia</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Acadomia France</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>French educational support network — 110 centers, 22,000 teachers. Hybrid online/offline tutoring from primary to higher education. News often in French.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,9 +525,16 @@
           <t>Act Inc</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ACT, ACT Education, Encoura, ACT/Encoura</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Do NOT confuse with ACT therapy (Acceptance Commitment Therapy), Bio-Manguinhos, or unrelated 'ACT' news</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -532,9 +542,6 @@
           <t>Acuity Insights</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -542,9 +549,6 @@
           <t>Al-Mansour University College</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -552,9 +556,6 @@
           <t>Alinea International</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,9 +563,11 @@
           <t>Aloha International</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mental arithmetic franchise for kids — Category C EdTech. NOT Hawaii / Aloha state-related news</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -572,9 +575,11 @@
           <t>American Council on Education</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -582,9 +587,16 @@
           <t>American Council on the Teaching of Foreign Languages</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ACTFL, ACTFL Language Centre, Language Connects Foundation, LCF, ACTFL Proficiency Tests, OPI, WPT, AAPPL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Professional standards body and assessment provider for language educators. Track proficiency test news (OPI, WPT, AAPPL), certifications, partnerships with universities/governments, and standard-setting initiatives. Includes Language Connects Foundation (LCF) as charitable arm.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -592,9 +604,11 @@
           <t>American Institutes for Research</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -602,9 +616,6 @@
           <t>American University of Cairo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -612,9 +623,11 @@
           <t>Apollo</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Apollo Education Group ONLY (operates University of Phoenix). NOT Apollo private equity, Apollo Global Management, or Apollo Hospitals</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -622,9 +635,11 @@
           <t>ApplyBoard</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ApplyBoard Inc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -632,9 +647,11 @@
           <t>Aptis</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aptis ESOL, British Council Aptis</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -642,9 +659,11 @@
           <t>Ascend Learning</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ascend Learning LLC, ATI Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -652,9 +671,6 @@
           <t>Association of Commonwealth Universities</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -662,9 +678,11 @@
           <t>Australian Council for Educational Research</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -672,9 +690,6 @@
           <t>Avant</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +697,16 @@
           <t>BYJU's</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BYJUs, Think and Learn, Aakash, Aakash BYJU's</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Heavy regulatory/legal news — keep all lawsuit, insolvency, NCLT, layoffs, and investor dispute updates</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -692,9 +714,11 @@
           <t>Babbel</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Babbel GmbH, Babbel.com</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -702,9 +726,16 @@
           <t>Babington Education</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Babington English, Babington HK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hong Kong-based English learning centre for children K1-P6. Largest provider of Ruth Miskin's RWI phonics programme in HK. NOT to be confused with UK-based Babington apprenticeship provider.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -712,9 +743,6 @@
           <t>Be Studio</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -722,9 +750,6 @@
           <t>BenchPrep</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -732,9 +757,16 @@
           <t>Berlitz</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Berlitz Corporation, Berlitz Languages</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Owned by Benesse. Category A. Often appears in Japanese-language sources</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -742,9 +774,16 @@
           <t>British Council</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>British Council UK, BC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Primary BC tracking — keep all IELTS, Aptis, English teaching, study UK, cultural engagement, scholarship, grant, partnership news</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -752,9 +791,6 @@
           <t>British Institutes</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -762,9 +798,6 @@
           <t>British School Group</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -772,9 +805,6 @@
           <t>British University of Bahrain</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -782,9 +812,11 @@
           <t>Busuu</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Busuu Online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -792,9 +824,16 @@
           <t>Byron Elementary School</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Byron Elementary, Byron ES</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Small public elementary school in Byron, Georgia (614 students, PK-5). Limited news volume — most news will likely be hyperlocal community activity (Tier 3 → Reject). Keep only if part of a strategic EdTech pilot, statewide program, or major partnership. Default toward REVIEW so nothing relevant is missed.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -802,9 +841,11 @@
           <t>CELPip/Paragon</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CELPIP, Paragon Testing, Paragon Testing Enterprises</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -812,9 +853,6 @@
           <t>Cambium Learning Group</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -822,9 +860,11 @@
           <t>Cambly</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cambly Inc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -832,9 +872,16 @@
           <t>Cambridge Assessment International Education</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cambridge International, CAIE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exams body — Category B. Owned by Cambridge University Press &amp; Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -842,9 +889,16 @@
           <t>Cambridge English</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cambridge English Language Assessment, Cambridge ESOL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cambridge English (teaching) — Category A. Differentiate from Cambridge Assessment (Category B) and Cambridge University Press &amp; Assessment (Category B)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -852,9 +906,16 @@
           <t>Cambridge University Press &amp; Assessment</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cambridge University Press, CUP, Cambridge Assessment</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Multi-business. Publishing arm overlaps with EdTech (Category C). Default to Category B for exam/assessment news</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -862,9 +923,6 @@
           <t>Capman Testing Solutions</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -872,9 +930,6 @@
           <t>Capti Voice</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -882,9 +937,6 @@
           <t>Care International</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -892,9 +944,11 @@
           <t>Carnegie Foundation for the Advancement of Teaching</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Connected to Carnegie Hero Fund. Track education innovation programs</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -902,9 +956,11 @@
           <t>Cengage</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cengage Group, Cengage Learning, National Geographic Learning</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -912,9 +968,16 @@
           <t>Chan Zuckerberg Initiative</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CZI</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Education + science. The Primary School closure is recent news</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -922,9 +985,6 @@
           <t>Chatterbug</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -932,9 +992,11 @@
           <t>Chegg</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chegg Inc</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -942,9 +1004,6 @@
           <t>Civica Assessments</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -952,9 +1011,6 @@
           <t>Class Technologies</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -962,9 +1018,6 @@
           <t>Cognia</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -972,9 +1025,11 @@
           <t>College Board</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>The College Board, SAT, AP</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -982,9 +1037,6 @@
           <t>CollegeDekho</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -992,9 +1044,16 @@
           <t>Cornerstone</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cornerstone OnDemand, CSOD</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cornerstone OnDemand (HR tech) ONLY. NOT Cornerstone Church, Cornerstone United Methodist, or Cornerstone preschools</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1002,9 +1061,16 @@
           <t>Coursera</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Coursera Inc, Coursera Plus</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recently merged with Udemy (2026). Track combined entity news</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1012,9 +1078,6 @@
           <t>Cowater International</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1022,9 +1085,6 @@
           <t>Creverse</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1032,9 +1092,6 @@
           <t>Criteria</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1042,9 +1099,11 @@
           <t>Cuemath</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cuemath Maths</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1052,9 +1111,6 @@
           <t>DMM English</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1062,9 +1118,6 @@
           <t>Data Recognition Corporation</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1072,9 +1125,11 @@
           <t>Degreed</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Degreed Inc</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1082,9 +1137,16 @@
           <t>Digital Promise</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Digital Promise Global</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>K-12 AI research, AIMS EduData grants, learner innovation</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1092,9 +1154,11 @@
           <t>Duolingo</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Duolingo Inc, Duo, Duolingo Max</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1102,9 +1166,16 @@
           <t>Duolingo English Test</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DET, Duolingo Test</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Track separately under Category B (Assessment), NOT Category A. For general Duolingo product/marketing news, use Category A</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1112,9 +1183,6 @@
           <t>ELS</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1122,9 +1190,16 @@
           <t>ELSA</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ELSA AI, ELSA Vietnam</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Vietnamese-origin AI English speaking app. Often appears in Vietnamese/Asian sources. Aliases include 'ELSA' (often used in shorter mentions).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1132,9 +1207,6 @@
           <t>EMG Education</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1142,9 +1214,16 @@
           <t>ETS</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Educational Testing Service, ETS Inc, ETS Global</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Parent organization (Educational Testing Service). Track ETS corporate news — leadership, financials, research, partnerships, M&amp;A, divestitures. Test-specific news (TOEFL, TOEIC) goes to dedicated entries. ETS acquired PSI Services (2023) — major M&amp;A news may overlap with PSI Services entry; classify under both if relevant.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1152,9 +1231,6 @@
           <t>Edforce</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1162,9 +1238,6 @@
           <t>Edgenuity</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1172,9 +1245,11 @@
           <t>Edmentum</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Edmentum Inc</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1182,9 +1257,6 @@
           <t>EduCanada</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1192,9 +1264,6 @@
           <t>Education &amp; Training Evaluation Commission</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1202,9 +1271,6 @@
           <t>Education Development Trust (EDT)</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1212,9 +1278,16 @@
           <t>Education First</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EF, EF Education First, EF English Live, EF EPI</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EF has multiple sub-brands: EF English Live, EFSet, Hult International Business School. All map to Category A</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1222,9 +1295,6 @@
           <t>EducationUSA</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1232,9 +1302,6 @@
           <t>Edventure School</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1242,9 +1309,6 @@
           <t>Edwin</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1252,9 +1316,11 @@
           <t>Eightfold AI</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Eightfold, Eightfold.ai</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1262,9 +1328,11 @@
           <t>Eiken Foundation of Japan</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Eiken</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1272,9 +1340,11 @@
           <t>English First</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EF, EF English First</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1282,9 +1352,6 @@
           <t>English Kids Academy</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1292,9 +1359,6 @@
           <t>EnglishDom</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1302,9 +1366,6 @@
           <t>Europalso</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1312,9 +1373,6 @@
           <t>Europe Schools</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1322,9 +1380,6 @@
           <t>Exams Andalucía</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1332,9 +1387,6 @@
           <t>Eye Level</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1342,9 +1394,6 @@
           <t>FHI 360</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1352,9 +1401,6 @@
           <t>First Cambridge Education Centre</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1362,9 +1408,6 @@
           <t>Five-Star E-Learning (FSEL)</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1372,9 +1415,6 @@
           <t>Frontline</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1382,9 +1422,11 @@
           <t>Fuel50</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fuel50 Inc</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1392,9 +1434,16 @@
           <t>Gates Foundation</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bill &amp; Melinda Gates Foundation, BMGF, Gates</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Often funds K-12 reform, AI tutoring, higher-ed access programs. Big tracked partner for both BC and ETS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1402,9 +1451,11 @@
           <t>Glossika</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Glossika AI</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1412,9 +1463,6 @@
           <t>GoFluent</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1422,9 +1470,16 @@
           <t>GoGuardian</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Go Guardian, GoGuardian Inc, Pear Deck Learning</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Now part of Pear Deck Learning ecosystem. Track both brand names</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1432,9 +1487,11 @@
           <t>Goethe Institute</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Goethe-Institut, Goethe Institut</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1442,9 +1499,11 @@
           <t>Graduate Management Admission Council</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GMAC, GMAT</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1452,9 +1511,6 @@
           <t>Great Little People</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1462,9 +1518,6 @@
           <t>Green Forest School</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1472,9 +1525,16 @@
           <t>HMH (Houghton Mifflin Harcourt )</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HMH, Houghton Mifflin Harcourt, HMH Inc, HMH Labs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Acquired Writable; launched HMH Labs for K-12 emerging tech</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1482,9 +1542,11 @@
           <t>Handshake</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Joinhandshake</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1492,9 +1554,11 @@
           <t>Harver</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Harver Inc</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1502,9 +1566,11 @@
           <t>Helen Doron</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Helen Doron English, Helen Doron Educational Group</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1512,9 +1578,6 @@
           <t>Hellenic American Union (HAU)</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1522,9 +1585,11 @@
           <t>HelloTalk</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HelloTalk Inc</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1532,9 +1597,6 @@
           <t>Higher Education Admission Center (Oman)</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1542,9 +1604,6 @@
           <t>Hirevue</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1552,9 +1611,6 @@
           <t>Hogan</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1562,9 +1618,6 @@
           <t>IALF Education for Development</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1572,9 +1625,16 @@
           <t>IDP</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IDP Education, IDP Australia</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Multi-business: study abroad placement + IELTS co-ownership. Default Category D for placement/recruitment news; Category B for IELTS news</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1582,9 +1642,16 @@
           <t>IDP IELTS</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IDP IELTS Australia</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Specifically IELTS arm of IDP — Category B (Assessment)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1592,9 +1659,16 @@
           <t>IELTS</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>International English Language Testing System</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Co-owned by British Council, IDP, and Cambridge Assessment. Default Category B (Assessment)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1602,9 +1676,6 @@
           <t>IELTSMaterial</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1612,9 +1683,11 @@
           <t>IH (International House)</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>International House, IH World, IH Bristol</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1622,9 +1695,6 @@
           <t>Inlingua</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1632,9 +1702,6 @@
           <t>Inspera</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1642,9 +1709,6 @@
           <t>Instituto Cervantes (Cervantes Institute of Rabat)</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1652,9 +1716,11 @@
           <t>International Baccalaureate (IB)</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IB, International Baccalaureate Organization, IBO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1662,9 +1728,6 @@
           <t>International House Yangon</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1672,9 +1735,11 @@
           <t>International Rescue Committee</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IRC</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1682,9 +1747,6 @@
           <t>International Test Center (ITC)</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1692,9 +1754,6 @@
           <t>International Test of English Proficiency</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1702,9 +1761,11 @@
           <t>Italki</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>italki Inc</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1712,9 +1773,6 @@
           <t>Janison</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1722,9 +1780,6 @@
           <t>Jobs for the Future</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1732,9 +1787,6 @@
           <t>Julia Gabriel</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1742,9 +1794,6 @@
           <t>KPZ University of Applied Sciences</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1752,9 +1801,11 @@
           <t>Kaplan International</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Kaplan, Kaplan Inc, Kaplan Professional</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1762,9 +1813,6 @@
           <t>Kawai Juku</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1772,9 +1820,6 @@
           <t>Kelly Education</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1782,9 +1827,11 @@
           <t>Kids&amp;Us</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Kids and Us, Kids&amp;Us English</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1792,9 +1839,6 @@
           <t>Kira Talent</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1802,9 +1846,6 @@
           <t>Knowledgemotion</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1812,9 +1853,6 @@
           <t>Kumon</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1822,9 +1860,6 @@
           <t>La Casita De Ingles</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1832,9 +1867,6 @@
           <t>Lang LTC Language School</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1842,9 +1874,6 @@
           <t>Language Link</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1852,9 +1881,11 @@
           <t>LanguageCert</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LanguageCert International ESOL</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1862,9 +1893,11 @@
           <t>Law School Admission Council</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>LSAC, LSAT</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1872,9 +1905,6 @@
           <t>Learnlight</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1882,9 +1912,6 @@
           <t>Learnosity</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1892,9 +1919,6 @@
           <t>Learnship</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1902,9 +1926,16 @@
           <t>Les Petits Biligues</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Les Petits Biligues (vendor typo), LPB</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>French brand teaching English to children. Also offers babysitting and tutoring through Nanny Agency &amp; Academy Services. Vendor data sometimes contains typo 'Biligues' (missing 'n') — agent should recognize both spellings.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1912,9 +1943,11 @@
           <t>LingQ</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>LingQ App</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1922,9 +1955,11 @@
           <t>Lingoda</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lingoda GmbH</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1932,9 +1967,11 @@
           <t>Lingokids</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lingokids Spain</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1942,9 +1979,6 @@
           <t>LinguaSkill</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1952,9 +1986,6 @@
           <t>Lingvist</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1962,9 +1993,6 @@
           <t>Little Fox</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1972,9 +2000,16 @@
           <t>Liulishuo</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>LAIX, English Liulishuo, Liulishuo AI</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Chinese AI English company (LAIX). Often appears in Chinese-language sources</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1982,9 +2017,11 @@
           <t>Macmillan Education</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Macmillan</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1992,9 +2029,11 @@
           <t>Malaysian University English Test</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MUET, Majlis Peperiksaan Malaysia</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2002,9 +2041,16 @@
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation, Mastercard Inc</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Track ONLY education/CSR/scholarship/foundation news. Auto-reject all payments/core business news via Layer 4 pre-filter</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2012,9 +2058,11 @@
           <t>McGraw Hill</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>McGraw-Hill, McGraw Hill Education</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2022,9 +2070,6 @@
           <t>Measurement Inc</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2032,9 +2077,6 @@
           <t>Meazure Learning</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2042,9 +2084,6 @@
           <t>Memorang</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2052,9 +2091,11 @@
           <t>Memrise</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Memrise App</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2062,9 +2103,6 @@
           <t>MeritTrac</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2072,9 +2110,6 @@
           <t>Michigan English Test</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2082,9 +2117,11 @@
           <t>Michigan Language Assessment (Cambridge Michigan Language Assessment)</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CaMLA</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2092,9 +2129,6 @@
           <t>Ministry of Education (Oman)</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2102,9 +2136,6 @@
           <t>Ministry of Higher Education (Oman)</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2112,9 +2143,11 @@
           <t>Mondly</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Mondly by Pearson</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2122,9 +2155,6 @@
           <t>Mpower Financing</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2132,9 +2162,6 @@
           <t>Muscat University</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2142,9 +2169,6 @@
           <t>NIRAS</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2152,9 +2176,6 @@
           <t>NTUC Learning Hub</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2162,9 +2183,11 @@
           <t>NWEA</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Northwest Evaluation Association, MAP Growth, MAP Reading</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2172,9 +2195,6 @@
           <t>National Assessment of Educational Progress</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2182,9 +2202,6 @@
           <t>National Skills Coalition</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2192,9 +2209,6 @@
           <t>National University of Science &amp; Technology</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2202,9 +2216,6 @@
           <t>Noredink</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2212,9 +2223,6 @@
           <t>Noun Town</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2222,9 +2230,6 @@
           <t>Novakid</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2232,9 +2237,6 @@
           <t>Number 16 School</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2242,9 +2244,6 @@
           <t>Oak National Academy</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2252,9 +2251,11 @@
           <t>Occupational English Test</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OET, Cambridge Boxhill</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2262,9 +2263,11 @@
           <t>Open English</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Open English LLC</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2272,9 +2275,16 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ChatGPT, GPT, GPT-4, GPT-5, Codex, Sora, DALL-E, OpenAI Academy, OpenAI Education</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Keep product launches, AI features, partnerships, client wins, senior hires, regulatory, M&amp;A, education-deployment news</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2282,9 +2292,6 @@
           <t>OpenClassrooms</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2292,9 +2299,6 @@
           <t>Opportunity@Work</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2302,9 +2306,6 @@
           <t>Options Consulting Services</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2312,9 +2313,16 @@
           <t>Organisation for Economic Co-operation and Development</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>OECD, Organization for Economic Cooperation and Development, PISA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>PISA assessment is high-priority — overlap with Category B context</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2322,9 +2330,11 @@
           <t>Orijin</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Corrections/re-entry edtech (public benefit corp). Flag overlap with social impact / education equity themes</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2332,9 +2342,6 @@
           <t>Overdeck Family Foundation</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2342,9 +2349,11 @@
           <t>Oxford AQA</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>OxfordAQA International</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2352,9 +2361,6 @@
           <t>Oxford Policy Management</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2362,9 +2368,6 @@
           <t>Oxford Test of English</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2372,9 +2375,11 @@
           <t>Oxford University Press</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>OUP, OUP Mexico, Oxford University Press Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2382,9 +2387,11 @@
           <t>PDK</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PDK International</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2392,9 +2399,11 @@
           <t>PSI Services</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Test delivery and proctoring services. Acquired by ETS in 2023 — major M&amp;A, leadership, or strategic news may overlap with ETS entry; classify under both if relevant.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2402,9 +2411,6 @@
           <t>Paper Rater</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2412,9 +2418,6 @@
           <t>Password English Language Testing</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2422,9 +2425,16 @@
           <t>Pear Deck Tutor (TutorMe)</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TutorMe, Pear Deck</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Formerly TutorMe, now part of Pear Deck Learning. Track both names</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2432,9 +2442,16 @@
           <t>Pearson</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Pearson plc, Pearson Education, Pearson Higher Ed</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Pearson is multi-business. Pearson Education = Category C; Pearson PTE = Category B. Default to Category C unless article is specifically about PTE assessment</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2442,9 +2459,11 @@
           <t>Pearson PTE</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PTE, PTE Academic, PTE Core, Pearson Test of English</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2452,9 +2471,11 @@
           <t>Phenom</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Phenom People, PhenomPeople</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2462,9 +2483,6 @@
           <t>Pipplet</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2472,9 +2490,11 @@
           <t>Planet Spark</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PlanetSpark</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2482,9 +2502,6 @@
           <t>Platzi</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2492,9 +2509,11 @@
           <t>PowerSchool</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PowerSchool Group, PowerSchool LMS</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2502,9 +2521,11 @@
           <t>Preply</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Preply Inc</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2512,9 +2533,11 @@
           <t>Princeton Review</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>The Princeton Review</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2522,9 +2545,11 @@
           <t>Prometric</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Prometric LLC</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2532,9 +2557,6 @@
           <t>Public Consulting Group</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2542,9 +2564,16 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers, PwC Global, PwC Foundation</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Track ONLY education/CSR/workforce-skills/sustainability news. Auto-reject all consulting/audit/advisory news via Layer 4 pre-filter</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2552,9 +2581,6 @@
           <t>Qatar Aeronautical Academy</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2562,9 +2588,6 @@
           <t>Qatar Foundation</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2572,9 +2595,11 @@
           <t>Quizlet</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Quizlet Inc</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2582,9 +2607,6 @@
           <t>RTI International</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2592,9 +2614,6 @@
           <t>Rarejob</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2602,9 +2621,6 @@
           <t>Risr</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2612,9 +2628,11 @@
           <t>Rosetta Stone</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Rosetta Stone Inc, IXL Learning</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2622,9 +2640,11 @@
           <t>SHL</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SHL Group, SHL.com</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2632,9 +2652,6 @@
           <t>Savvas Learning</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2642,9 +2659,6 @@
           <t>Shakespeare School</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2652,9 +2666,6 @@
           <t>Singapore Institute of Management (SIM)</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2662,9 +2673,6 @@
           <t>Skyeng</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2672,9 +2680,6 @@
           <t>So Easy</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2682,9 +2687,16 @@
           <t>Speexx</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Speexx GmbH, Speexx Coaching</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Independent people development platform offering digital business coaching and AI-powered language training for global workforce. 8M+ users, 1,500+ enterprise clients. Munich-based. Strong B2B/corporate language training presence — track enterprise wins, AI coaching innovations, partnerships.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2692,9 +2704,6 @@
           <t>Study.com</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2702,9 +2711,6 @@
           <t>Superprof</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2712,9 +2718,6 @@
           <t>Surpass Powering Assessment</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2722,9 +2725,11 @@
           <t>Symplicity</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Symplicity Corporation</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2732,9 +2737,11 @@
           <t>TCS ION National Qualifier Test</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TCS NQT, TCS iON</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2742,9 +2749,6 @@
           <t>TELC</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2752,9 +2756,16 @@
           <t>TES</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Times Educational Supplement, TES Global, tes.com</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Global education company offering software (timetabling, SEND, behaviour management, staff wellbeing), teaching materials platform, online magazine, recruitment services, and teacher training. UK-rooted but global.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2762,9 +2773,16 @@
           <t>TOEFL/ETS</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TOEFL, ETS, Educational Testing Service, TOEFL iBT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>ETS is parent. Keep all TOEFL test news, ETS product launches, ETS acquisitions (e.g., PSI), and ETS research. For pure ETS corporate news, use the standalone ETS entry.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2772,9 +2790,16 @@
           <t>TOEIC/ETS</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TOEIC, ETS, Test of English for International Communication</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>TOEIC is an ETS product. Treat similarly to TOEFL/ETS. For pure ETS corporate news, use the standalone ETS entry.</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2782,9 +2807,6 @@
           <t>Talland College</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2792,9 +2814,11 @@
           <t>Talogy</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Talogy Inc (formerly PSI Talent Management)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2802,9 +2826,6 @@
           <t>Talview</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2812,9 +2833,6 @@
           <t>Teachers Pay Teachers</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2822,9 +2840,6 @@
           <t>TeamCo​</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2832,9 +2847,6 @@
           <t>Teddy Eddie</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2842,9 +2854,11 @@
           <t>Test Gorilla</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TestGorilla</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2852,9 +2866,6 @@
           <t>Test reach</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2862,9 +2873,6 @@
           <t>Tetra Tech</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2872,9 +2880,6 @@
           <t>The Bridge</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2882,9 +2887,11 @@
           <t>The French Institute (Institut Français)</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Institut Français, French Institute</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2892,9 +2899,16 @@
           <t>The World Bank</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>World Bank, WB, World Bank Group, IBRD</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Keep education loans, skills loans, capacity-building grants. Review infrastructure loans only if human-capital angle exists</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2902,9 +2916,6 @@
           <t>Tracktest</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2912,9 +2923,11 @@
           <t>Trinity College London</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Trinity College, Trinity ESOL</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2922,9 +2935,11 @@
           <t>Turnitin</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Turnitin LLC, iThenticate</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2932,9 +2947,6 @@
           <t>Twinkle Star</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2942,9 +2954,11 @@
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Unacademy Group</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2952,9 +2966,11 @@
           <t>Unicef</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>United Nations Children's Fund</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2962,9 +2978,6 @@
           <t>Unihouse</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2972,9 +2985,16 @@
           <t>United Nations Educational Scientific and Cultural Organization</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>UNESCO</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Multilateral body. Keep all education/cultural/scholarship/literacy/youth/teacher-training/MIL programs</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -2982,9 +3002,11 @@
           <t>Universities UK</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>UUK, Universities UK International</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -2992,9 +3014,6 @@
           <t>University of Babylon</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3002,9 +3021,11 @@
           <t>University of Cambridge</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Cambridge University</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3012,9 +3033,6 @@
           <t>University of Doha for Science and Technology</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3022,9 +3040,6 @@
           <t>University of Duhok</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3032,9 +3047,6 @@
           <t>University of Kurdistan Hewler (UKH)</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3042,9 +3054,6 @@
           <t>University of Lincoln</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3052,9 +3061,6 @@
           <t>University of Sulaimani (UoS)</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3062,9 +3068,6 @@
           <t>University of Technology and Applied Sciences (UTAS)</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3072,9 +3075,6 @@
           <t>University of Wollongong</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3082,9 +3082,6 @@
           <t>Unlimited Instruction</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3092,9 +3089,11 @@
           <t>UpGrad</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>upGrad Enterprise, upGrad School of Technology (uGSOT)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3102,9 +3101,11 @@
           <t>Upwork</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Upwork Inc, Upwork Global</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3112,9 +3113,16 @@
           <t>VIPKid</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>VIP Kid, VIPKid Global</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Online English for kids, primarily Chinese market. Often appears in Chinese/Korean sources</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3122,9 +3130,6 @@
           <t>VUS</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3132,9 +3137,6 @@
           <t>Vantage Learning</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3142,9 +3144,6 @@
           <t>Vaughan</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3152,9 +3151,11 @@
           <t>Vedantu</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Vedantu Innovations</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3162,9 +3163,6 @@
           <t>Versant</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3172,9 +3170,11 @@
           <t>Wall Street English</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>WSE, Wall Street Institute</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3182,9 +3182,16 @@
           <t>Walton Family Foundation</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>WFF</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>K-12 charter schools, education research. Track Gen Z surveys with Gallup</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3192,9 +3199,11 @@
           <t>WestEd</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>West Ed</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3202,9 +3211,11 @@
           <t>Westat</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Westat Inc</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3212,9 +3223,11 @@
           <t>Workera</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Workera AI</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3222,9 +3235,6 @@
           <t>YBM Education</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3232,9 +3242,6 @@
           <t>eDynamic Learning</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3242,9 +3249,6 @@
           <t>iCEV</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3252,9 +3256,11 @@
           <t>iTEP</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>International Test of English Proficiency, iTEP International, iTEP Slate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3303,7 +3309,6 @@
           <t>Albanian</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3316,7 +3321,6 @@
           <t>Arabic, French</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3329,7 +3333,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3342,7 +3345,6 @@
           <t>English</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3355,7 +3357,6 @@
           <t>German</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3368,7 +3369,6 @@
           <t>Azerbaijani</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3381,7 +3381,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3394,7 +3393,6 @@
           <t>Portuguese</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3407,7 +3405,6 @@
           <t>Malay, English</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3420,7 +3417,6 @@
           <t>Bulgarian</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3433,7 +3429,6 @@
           <t>Khmer</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3446,7 +3441,6 @@
           <t>English, French</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3459,7 +3453,6 @@
           <t>Catalan, Spanish</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3472,7 +3465,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3485,7 +3477,6 @@
           <t>Chinese (Mandarin)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3498,7 +3489,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3511,7 +3501,6 @@
           <t>Croatian</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3524,7 +3513,6 @@
           <t>Greek, Turkish</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3537,7 +3525,6 @@
           <t>Czech</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3550,7 +3537,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3563,7 +3549,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3576,7 +3561,6 @@
           <t>Estonian</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3589,7 +3573,6 @@
           <t>French</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3602,7 +3585,6 @@
           <t>Georgian</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3615,7 +3597,6 @@
           <t>German</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3628,7 +3609,6 @@
           <t>Greek</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3641,7 +3621,6 @@
           <t>Chinese (Cantonese), English</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3654,7 +3633,6 @@
           <t>Hungarian</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3667,7 +3645,6 @@
           <t>Hindi, English</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3680,7 +3657,6 @@
           <t>Indonesian</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3693,7 +3669,6 @@
           <t>Persian (Farsi)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3706,7 +3681,6 @@
           <t>Arabic, Kurdish</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3719,7 +3693,6 @@
           <t>English, Irish</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3732,7 +3705,6 @@
           <t>Hebrew, Arabic</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3745,7 +3717,6 @@
           <t>Italian</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3758,7 +3729,6 @@
           <t>Japanese</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3771,7 +3741,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3784,7 +3753,6 @@
           <t>Kazakh, Russian</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3797,7 +3765,6 @@
           <t>Korean</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3810,7 +3777,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3823,7 +3789,6 @@
           <t>Arabic, French</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3836,7 +3801,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3849,7 +3813,6 @@
           <t>Malay, English</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3862,7 +3825,6 @@
           <t>English, French</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3875,7 +3837,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3888,7 +3849,6 @@
           <t>Montenegrin</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3901,7 +3861,6 @@
           <t>Arabic, French</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3914,7 +3873,6 @@
           <t>Burmese</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3927,7 +3885,6 @@
           <t>Nepali</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3940,7 +3897,6 @@
           <t>Dutch</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3953,7 +3909,6 @@
           <t>English</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3966,7 +3921,6 @@
           <t>English</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3979,7 +3933,6 @@
           <t>Macedonian</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3992,7 +3945,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4005,7 +3957,6 @@
           <t>Urdu, English</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4018,7 +3969,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4031,7 +3981,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4044,7 +3993,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4057,7 +4005,6 @@
           <t>Filipino, English</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4070,7 +4017,6 @@
           <t>Polish</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4083,7 +4029,6 @@
           <t>Portuguese</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4096,7 +4041,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4109,7 +4053,6 @@
           <t>Romanian</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4122,7 +4065,6 @@
           <t>Russian</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4135,7 +4077,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4148,7 +4089,6 @@
           <t>English, Mandarin, Malay</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4161,7 +4101,6 @@
           <t>Slovak</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4174,7 +4113,6 @@
           <t>English, Zulu, Afrikaans</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4187,7 +4125,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4200,7 +4137,6 @@
           <t>Sinhala, Tamil</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4213,7 +4149,6 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4226,7 +4161,6 @@
           <t>Mandarin Chinese</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4239,7 +4173,6 @@
           <t>Thai</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4252,7 +4185,6 @@
           <t>Arabic, French</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4265,7 +4197,6 @@
           <t>Turkish</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4278,7 +4209,6 @@
           <t>Arabic, English</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4291,7 +4221,6 @@
           <t>English</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4304,7 +4233,6 @@
           <t>English</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4317,7 +4245,6 @@
           <t>Ukrainian</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4330,7 +4257,6 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4343,7 +4269,6 @@
           <t>Uzbek</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4356,7 +4281,6 @@
           <t>Vietnamese</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/edtech-news-tracker/edtech_tracking_list.xlsx
+++ b/edtech-news-tracker/edtech_tracking_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:G281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -433,6 +433,8 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,6 +463,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Category Code</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Category Name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +485,16 @@
           <t>ABA</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -480,6 +502,16 @@
           <t>ABC Pathways School</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -487,6 +519,16 @@
           <t>ABT Global</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -494,6 +536,16 @@
           <t>AMIDEAST</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -501,6 +553,16 @@
           <t>Abdulla Al Ghurair Foundation</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -518,6 +580,16 @@
           <t>French educational support network — 110 centers, 22,000 teachers. Hybrid online/offline tutoring from primary to higher education. News often in French.</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,6 +607,16 @@
           <t>Do NOT confuse with ACT therapy (Acceptance Commitment Therapy), Bio-Manguinhos, or unrelated 'ACT' news</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -542,6 +624,16 @@
           <t>Acuity Insights</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -549,6 +641,16 @@
           <t>Al-Mansour University College</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -556,6 +658,16 @@
           <t>Alinea International</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -568,6 +680,16 @@
           <t>Mental arithmetic franchise for kids — Category C EdTech. NOT Hawaii / Aloha state-related news</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -580,6 +702,16 @@
           <t>ACE</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -597,6 +729,16 @@
           <t>Professional standards body and assessment provider for language educators. Track proficiency test news (OPI, WPT, AAPPL), certifications, partnerships with universities/governments, and standard-setting initiatives. Includes Language Connects Foundation (LCF) as charitable arm.</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -609,6 +751,16 @@
           <t>AIR</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -616,6 +768,16 @@
           <t>American University of Cairo</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -628,6 +790,16 @@
           <t>Apollo Education Group ONLY (operates University of Phoenix). NOT Apollo private equity, Apollo Global Management, or Apollo Hospitals</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -640,6 +812,16 @@
           <t>ApplyBoard Inc</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -652,6 +834,16 @@
           <t>Aptis ESOL, British Council Aptis</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -664,6 +856,16 @@
           <t>Ascend Learning LLC, ATI Nursing</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -671,6 +873,16 @@
           <t>Association of Commonwealth Universities</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -683,6 +895,16 @@
           <t>ACER</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -690,6 +912,16 @@
           <t>Avant</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -707,6 +939,16 @@
           <t>Heavy regulatory/legal news — keep all lawsuit, insolvency, NCLT, layoffs, and investor dispute updates</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -719,6 +961,16 @@
           <t>Babbel GmbH, Babbel.com</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -736,6 +988,16 @@
           <t>Hong Kong-based English learning centre for children K1-P6. Largest provider of Ruth Miskin's RWI phonics programme in HK. NOT to be confused with UK-based Babington apprenticeship provider.</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -743,6 +1005,16 @@
           <t>Be Studio</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -750,6 +1022,16 @@
           <t>BenchPrep</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -767,6 +1049,16 @@
           <t>Owned by Benesse. Category A. Often appears in Japanese-language sources</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -784,6 +1076,16 @@
           <t>Primary BC tracking — keep all IELTS, Aptis, English teaching, study UK, cultural engagement, scholarship, grant, partnership news</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -791,6 +1093,16 @@
           <t>British Institutes</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -798,6 +1110,16 @@
           <t>British School Group</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -805,6 +1127,16 @@
           <t>British University of Bahrain</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -817,6 +1149,16 @@
           <t>Busuu Online</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -834,6 +1176,16 @@
           <t>Small public elementary school in Byron, Georgia (614 students, PK-5). Limited news volume — most news will likely be hyperlocal community activity (Tier 3 → Reject). Keep only if part of a strategic EdTech pilot, statewide program, or major partnership. Default toward REVIEW so nothing relevant is missed.</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -846,6 +1198,16 @@
           <t>CELPIP, Paragon Testing, Paragon Testing Enterprises</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -853,6 +1215,16 @@
           <t>Cambium Learning Group</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -865,6 +1237,16 @@
           <t>Cambly Inc</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -882,6 +1264,16 @@
           <t>Exams body — Category B. Owned by Cambridge University Press &amp; Assessment</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -899,6 +1291,16 @@
           <t>Cambridge English (teaching) — Category A. Differentiate from Cambridge Assessment (Category B) and Cambridge University Press &amp; Assessment (Category B)</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -916,6 +1318,16 @@
           <t>Multi-business. Publishing arm overlaps with EdTech (Category C). Default to Category B for exam/assessment news</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -923,6 +1335,16 @@
           <t>Capman Testing Solutions</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -930,6 +1352,16 @@
           <t>Capti Voice</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -937,6 +1369,16 @@
           <t>Care International</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -949,6 +1391,16 @@
           <t>Connected to Carnegie Hero Fund. Track education innovation programs</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -961,6 +1413,16 @@
           <t>Cengage Group, Cengage Learning, National Geographic Learning</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -978,6 +1440,16 @@
           <t>Education + science. The Primary School closure is recent news</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -985,6 +1457,16 @@
           <t>Chatterbug</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -997,6 +1479,16 @@
           <t>Chegg Inc</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1004,6 +1496,16 @@
           <t>Civica Assessments</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1011,6 +1513,16 @@
           <t>Class Technologies</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1018,6 +1530,16 @@
           <t>Cognia</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1030,6 +1552,16 @@
           <t>The College Board, SAT, AP</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1037,6 +1569,16 @@
           <t>CollegeDekho</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1054,6 +1596,16 @@
           <t>Cornerstone OnDemand (HR tech) ONLY. NOT Cornerstone Church, Cornerstone United Methodist, or Cornerstone preschools</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1071,6 +1623,16 @@
           <t>Recently merged with Udemy (2026). Track combined entity news</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1078,6 +1640,16 @@
           <t>Cowater International</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1085,6 +1657,16 @@
           <t>Creverse</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1092,6 +1674,16 @@
           <t>Criteria</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1104,6 +1696,16 @@
           <t>Cuemath Maths</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1111,6 +1713,16 @@
           <t>DMM English</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1118,6 +1730,16 @@
           <t>Data Recognition Corporation</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1130,6 +1752,16 @@
           <t>Degreed Inc</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1147,6 +1779,16 @@
           <t>K-12 AI research, AIMS EduData grants, learner innovation</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1159,6 +1801,16 @@
           <t>Duolingo Inc, Duo, Duolingo Max</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1176,6 +1828,16 @@
           <t>Track separately under Category B (Assessment), NOT Category A. For general Duolingo product/marketing news, use Category A</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1183,6 +1845,16 @@
           <t>ELS</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1200,6 +1872,16 @@
           <t>Vietnamese-origin AI English speaking app. Often appears in Vietnamese/Asian sources. Aliases include 'ELSA' (often used in shorter mentions).</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1207,6 +1889,16 @@
           <t>EMG Education</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1224,6 +1916,16 @@
           <t>Parent organization (Educational Testing Service). Track ETS corporate news — leadership, financials, research, partnerships, M&amp;A, divestitures. Test-specific news (TOEFL, TOEIC) goes to dedicated entries. ETS acquired PSI Services (2023) — major M&amp;A news may overlap with PSI Services entry; classify under both if relevant.</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1231,6 +1933,16 @@
           <t>Edforce</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1238,6 +1950,16 @@
           <t>Edgenuity</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1250,6 +1972,16 @@
           <t>Edmentum Inc</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1257,6 +1989,16 @@
           <t>EduCanada</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1264,6 +2006,16 @@
           <t>Education &amp; Training Evaluation Commission</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1271,6 +2023,16 @@
           <t>Education Development Trust (EDT)</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1288,6 +2050,16 @@
           <t>EF has multiple sub-brands: EF English Live, EFSet, Hult International Business School. All map to Category A</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1295,6 +2067,16 @@
           <t>EducationUSA</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1302,6 +2084,16 @@
           <t>Edventure School</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1309,6 +2101,16 @@
           <t>Edwin</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1321,6 +2123,16 @@
           <t>Eightfold, Eightfold.ai</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1333,6 +2145,16 @@
           <t>Eiken</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1345,6 +2167,16 @@
           <t>EF, EF English First</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1352,6 +2184,16 @@
           <t>English Kids Academy</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1359,6 +2201,16 @@
           <t>EnglishDom</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1366,6 +2218,16 @@
           <t>Europalso</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1373,6 +2235,16 @@
           <t>Europe Schools</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1380,6 +2252,16 @@
           <t>Exams Andalucía</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1387,6 +2269,16 @@
           <t>Eye Level</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1394,6 +2286,16 @@
           <t>FHI 360</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1401,6 +2303,16 @@
           <t>First Cambridge Education Centre</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1408,6 +2320,16 @@
           <t>Five-Star E-Learning (FSEL)</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1415,6 +2337,16 @@
           <t>Frontline</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1427,6 +2359,16 @@
           <t>Fuel50 Inc</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1444,6 +2386,16 @@
           <t>Often funds K-12 reform, AI tutoring, higher-ed access programs. Big tracked partner for both BC and ETS</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1456,6 +2408,16 @@
           <t>Glossika AI</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1463,6 +2425,16 @@
           <t>GoFluent</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1480,6 +2452,16 @@
           <t>Now part of Pear Deck Learning ecosystem. Track both brand names</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1492,6 +2474,16 @@
           <t>Goethe-Institut, Goethe Institut</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1504,6 +2496,16 @@
           <t>GMAC, GMAT</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1511,6 +2513,16 @@
           <t>Great Little People</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1518,6 +2530,16 @@
           <t>Green Forest School</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1535,6 +2557,16 @@
           <t>Acquired Writable; launched HMH Labs for K-12 emerging tech</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1547,6 +2579,16 @@
           <t>Joinhandshake</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1559,6 +2601,16 @@
           <t>Harver Inc</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1571,6 +2623,16 @@
           <t>Helen Doron English, Helen Doron Educational Group</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1578,6 +2640,16 @@
           <t>Hellenic American Union (HAU)</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1590,6 +2662,16 @@
           <t>HelloTalk Inc</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1597,6 +2679,16 @@
           <t>Higher Education Admission Center (Oman)</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1604,6 +2696,16 @@
           <t>Hirevue</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1611,6 +2713,16 @@
           <t>Hogan</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1618,6 +2730,16 @@
           <t>IALF Education for Development</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1635,6 +2757,16 @@
           <t>Multi-business: study abroad placement + IELTS co-ownership. Default Category D for placement/recruitment news; Category B for IELTS news</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1652,6 +2784,16 @@
           <t>Specifically IELTS arm of IDP — Category B (Assessment)</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1669,6 +2811,16 @@
           <t>Co-owned by British Council, IDP, and Cambridge Assessment. Default Category B (Assessment)</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1676,6 +2828,16 @@
           <t>IELTSMaterial</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1688,6 +2850,16 @@
           <t>International House, IH World, IH Bristol</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1695,6 +2867,16 @@
           <t>Inlingua</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1702,6 +2884,16 @@
           <t>Inspera</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1709,6 +2901,16 @@
           <t>Instituto Cervantes (Cervantes Institute of Rabat)</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1721,6 +2923,16 @@
           <t>IB, International Baccalaureate Organization, IBO</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1728,6 +2940,16 @@
           <t>International House Yangon</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1740,6 +2962,16 @@
           <t>IRC</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1747,6 +2979,16 @@
           <t>International Test Center (ITC)</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1766,6 +3008,16 @@
           <t>italki Inc</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1773,6 +3025,16 @@
           <t>Janison</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1780,6 +3042,16 @@
           <t>Jobs for the Future</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1787,6 +3059,16 @@
           <t>Julia Gabriel</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1794,6 +3076,16 @@
           <t>KPZ University of Applied Sciences</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1806,6 +3098,16 @@
           <t>Kaplan, Kaplan Inc, Kaplan Professional</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1813,6 +3115,16 @@
           <t>Kawai Juku</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1820,6 +3132,16 @@
           <t>Kelly Education</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1832,6 +3154,16 @@
           <t>Kids and Us, Kids&amp;Us English</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1839,6 +3171,16 @@
           <t>Kira Talent</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1846,6 +3188,16 @@
           <t>Knowledgemotion</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1853,6 +3205,16 @@
           <t>Kumon</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1860,6 +3222,16 @@
           <t>La Casita De Ingles</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1867,6 +3239,16 @@
           <t>Lang LTC Language School</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1874,6 +3256,16 @@
           <t>Language Link</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1886,6 +3278,16 @@
           <t>LanguageCert International ESOL</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1898,6 +3300,16 @@
           <t>LSAC, LSAT</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1905,6 +3317,16 @@
           <t>Learnlight</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1912,6 +3334,16 @@
           <t>Learnosity</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1919,6 +3351,16 @@
           <t>Learnship</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1936,6 +3378,16 @@
           <t>French brand teaching English to children. Also offers babysitting and tutoring through Nanny Agency &amp; Academy Services. Vendor data sometimes contains typo 'Biligues' (missing 'n') — agent should recognize both spellings.</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1948,6 +3400,16 @@
           <t>LingQ App</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1960,6 +3422,16 @@
           <t>Lingoda GmbH</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1972,6 +3444,16 @@
           <t>Lingokids Spain</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1979,6 +3461,16 @@
           <t>LinguaSkill</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1986,6 +3478,16 @@
           <t>Lingvist</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1993,6 +3495,16 @@
           <t>Little Fox</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2010,6 +3522,16 @@
           <t>Chinese AI English company (LAIX). Often appears in Chinese-language sources</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2022,6 +3544,16 @@
           <t>Macmillan</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2034,6 +3566,16 @@
           <t>MUET, Majlis Peperiksaan Malaysia</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2051,6 +3593,16 @@
           <t>Track ONLY education/CSR/scholarship/foundation news. Auto-reject all payments/core business news via Layer 4 pre-filter</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Adjacent Corporate (tracked only for education/CSR angle)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2063,6 +3615,16 @@
           <t>McGraw-Hill, McGraw Hill Education</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2070,6 +3632,16 @@
           <t>Measurement Inc</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2077,6 +3649,16 @@
           <t>Meazure Learning</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2084,6 +3666,16 @@
           <t>Memorang</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2096,6 +3688,16 @@
           <t>Memrise App</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2103,6 +3705,16 @@
           <t>MeritTrac</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2110,6 +3722,16 @@
           <t>Michigan English Test</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2122,6 +3744,16 @@
           <t>CaMLA</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2129,6 +3761,16 @@
           <t>Ministry of Education (Oman)</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2136,6 +3778,16 @@
           <t>Ministry of Higher Education (Oman)</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2148,6 +3800,16 @@
           <t>Mondly by Pearson</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2155,6 +3817,16 @@
           <t>Mpower Financing</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2162,6 +3834,16 @@
           <t>Muscat University</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2169,6 +3851,16 @@
           <t>NIRAS</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2176,6 +3868,16 @@
           <t>NTUC Learning Hub</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2188,6 +3890,16 @@
           <t>Northwest Evaluation Association, MAP Growth, MAP Reading</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2195,6 +3907,16 @@
           <t>National Assessment of Educational Progress</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2202,6 +3924,16 @@
           <t>National Skills Coalition</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2209,6 +3941,16 @@
           <t>National University of Science &amp; Technology</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2216,6 +3958,16 @@
           <t>Noredink</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2223,6 +3975,16 @@
           <t>Noun Town</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2230,6 +3992,16 @@
           <t>Novakid</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2237,6 +4009,16 @@
           <t>Number 16 School</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2244,6 +4026,16 @@
           <t>Oak National Academy</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2256,6 +4048,16 @@
           <t>OET, Cambridge Boxhill</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2268,6 +4070,16 @@
           <t>Open English LLC</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2285,6 +4097,16 @@
           <t>Keep product launches, AI features, partnerships, client wins, senior hires, regulatory, M&amp;A, education-deployment news</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Technology &amp; Innovation</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2292,6 +4114,16 @@
           <t>OpenClassrooms</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2299,6 +4131,16 @@
           <t>Opportunity@Work</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2306,6 +4148,16 @@
           <t>Options Consulting Services</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2323,6 +4175,16 @@
           <t>PISA assessment is high-priority — overlap with Category B context</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2335,6 +4197,16 @@
           <t>Corrections/re-entry edtech (public benefit corp). Flag overlap with social impact / education equity themes</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2342,6 +4214,16 @@
           <t>Overdeck Family Foundation</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2354,6 +4236,16 @@
           <t>OxfordAQA International</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2361,6 +4253,16 @@
           <t>Oxford Policy Management</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2368,6 +4270,16 @@
           <t>Oxford Test of English</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2380,6 +4292,16 @@
           <t>OUP, OUP Mexico, Oxford University Press Mexico</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2392,6 +4314,16 @@
           <t>PDK International</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2404,6 +4336,16 @@
           <t>Test delivery and proctoring services. Acquired by ETS in 2023 — major M&amp;A, leadership, or strategic news may overlap with ETS entry; classify under both if relevant.</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2411,6 +4353,16 @@
           <t>Paper Rater</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2418,6 +4370,16 @@
           <t>Password English Language Testing</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2435,6 +4397,16 @@
           <t>Formerly TutorMe, now part of Pear Deck Learning. Track both names</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2452,6 +4424,16 @@
           <t>Pearson is multi-business. Pearson Education = Category C; Pearson PTE = Category B. Default to Category C unless article is specifically about PTE assessment</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2464,6 +4446,16 @@
           <t>PTE, PTE Academic, PTE Core, Pearson Test of English</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2476,6 +4468,16 @@
           <t>Phenom People, PhenomPeople</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2483,6 +4485,16 @@
           <t>Pipplet</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2495,6 +4507,16 @@
           <t>PlanetSpark</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2502,6 +4524,16 @@
           <t>Platzi</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2514,6 +4546,16 @@
           <t>PowerSchool Group, PowerSchool LMS</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2526,6 +4568,16 @@
           <t>Preply Inc</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2538,6 +4590,16 @@
           <t>The Princeton Review</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2550,6 +4612,16 @@
           <t>Prometric LLC</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2557,6 +4629,16 @@
           <t>Public Consulting Group</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2574,6 +4656,16 @@
           <t>Track ONLY education/CSR/workforce-skills/sustainability news. Auto-reject all consulting/audit/advisory news via Layer 4 pre-filter</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Adjacent Corporate (tracked only for education/CSR angle)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2581,6 +4673,16 @@
           <t>Qatar Aeronautical Academy</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2588,6 +4690,16 @@
           <t>Qatar Foundation</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2600,6 +4712,16 @@
           <t>Quizlet Inc</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2607,6 +4729,16 @@
           <t>RTI International</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2614,6 +4746,16 @@
           <t>Rarejob</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2621,6 +4763,16 @@
           <t>Risr</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2633,6 +4785,16 @@
           <t>Rosetta Stone Inc, IXL Learning</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2645,6 +4807,16 @@
           <t>SHL Group, SHL.com</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2652,6 +4824,16 @@
           <t>Savvas Learning</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2659,6 +4841,16 @@
           <t>Shakespeare School</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2666,6 +4858,16 @@
           <t>Singapore Institute of Management (SIM)</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2673,6 +4875,16 @@
           <t>Skyeng</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2680,6 +4892,16 @@
           <t>So Easy</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2697,6 +4919,16 @@
           <t>Independent people development platform offering digital business coaching and AI-powered language training for global workforce. 8M+ users, 1,500+ enterprise clients. Munich-based. Strong B2B/corporate language training presence — track enterprise wins, AI coaching innovations, partnerships.</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2704,6 +4936,16 @@
           <t>Study.com</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2711,6 +4953,16 @@
           <t>Superprof</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2718,6 +4970,16 @@
           <t>Surpass Powering Assessment</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2730,6 +4992,16 @@
           <t>Symplicity Corporation</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2742,6 +5014,16 @@
           <t>TCS NQT, TCS iON</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2749,6 +5031,16 @@
           <t>TELC</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2766,6 +5058,16 @@
           <t>Global education company offering software (timetabling, SEND, behaviour management, staff wellbeing), teaching materials platform, online magazine, recruitment services, and teacher training. UK-rooted but global.</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2783,6 +5085,16 @@
           <t>ETS is parent. Keep all TOEFL test news, ETS product launches, ETS acquisitions (e.g., PSI), and ETS research. For pure ETS corporate news, use the standalone ETS entry.</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2800,6 +5112,16 @@
           <t>TOEIC is an ETS product. Treat similarly to TOEFL/ETS. For pure ETS corporate news, use the standalone ETS entry.</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2807,6 +5129,16 @@
           <t>Talland College</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2819,6 +5151,16 @@
           <t>Talogy Inc (formerly PSI Talent Management)</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2826,6 +5168,16 @@
           <t>Talview</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2833,6 +5185,16 @@
           <t>Teachers Pay Teachers</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2840,6 +5202,16 @@
           <t>TeamCo​</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2847,6 +5219,16 @@
           <t>Teddy Eddie</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2859,6 +5241,16 @@
           <t>TestGorilla</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2866,6 +5258,16 @@
           <t>Test reach</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2873,6 +5275,16 @@
           <t>Tetra Tech</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2880,6 +5292,16 @@
           <t>The Bridge</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2892,6 +5314,16 @@
           <t>Institut Français, French Institute</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2909,6 +5341,16 @@
           <t>Keep education loans, skills loans, capacity-building grants. Review infrastructure loans only if human-capital angle exists</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2916,6 +5358,16 @@
           <t>Tracktest</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2928,6 +5380,16 @@
           <t>Trinity College, Trinity ESOL</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2940,6 +5402,16 @@
           <t>Turnitin LLC, iThenticate</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2947,6 +5419,16 @@
           <t>Twinkle Star</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2959,6 +5441,16 @@
           <t>Unacademy Group</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2971,6 +5463,16 @@
           <t>United Nations Children's Fund</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2978,6 +5480,16 @@
           <t>Unihouse</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2995,6 +5507,16 @@
           <t>Multilateral body. Keep all education/cultural/scholarship/literacy/youth/teacher-training/MIL programs</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3007,6 +5529,16 @@
           <t>UUK, Universities UK International</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3014,6 +5546,16 @@
           <t>University of Babylon</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3026,6 +5568,16 @@
           <t>Cambridge University</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3033,6 +5585,16 @@
           <t>University of Doha for Science and Technology</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3040,6 +5602,16 @@
           <t>University of Duhok</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3047,6 +5619,16 @@
           <t>University of Kurdistan Hewler (UKH)</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3054,6 +5636,16 @@
           <t>University of Lincoln</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3061,6 +5653,16 @@
           <t>University of Sulaimani (UoS)</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3068,6 +5670,16 @@
           <t>University of Technology and Applied Sciences (UTAS)</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3075,6 +5687,16 @@
           <t>University of Wollongong</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Higher Education / Study Abroad / University</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3094,6 +5716,16 @@
           <t>upGrad Enterprise, upGrad School of Technology (uGSOT)</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3106,6 +5738,16 @@
           <t>Upwork Inc, Upwork Global</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3123,6 +5765,16 @@
           <t>Online English for kids, primarily Chinese market. Often appears in Chinese/Korean sources</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3130,6 +5782,16 @@
           <t>VUS</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3137,6 +5799,16 @@
           <t>Vantage Learning</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3144,6 +5816,16 @@
           <t>Vaughan</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3156,6 +5838,16 @@
           <t>Vedantu Innovations</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3163,6 +5855,16 @@
           <t>Versant</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3175,6 +5877,16 @@
           <t>WSE, Wall Street Institute</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>English / Language Learning competitor</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3192,6 +5904,16 @@
           <t>K-12 charter schools, education research. Track Gen Z surveys with Gallup</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3204,6 +5926,16 @@
           <t>West Ed</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3216,6 +5948,16 @@
           <t>Westat Inc</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Cultural Engagement / NGO / Development / Foundation / Government body</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3228,6 +5970,16 @@
           <t>Workera AI</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Skills / Workforce / HR Tech / Talent Assessment</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3235,6 +5987,16 @@
           <t>YBM Education</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3242,6 +6004,16 @@
           <t>eDynamic Learning</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3249,6 +6021,16 @@
           <t>iCEV</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>EdTech / Online Learning / Publishing competitor</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3259,6 +6041,16 @@
       <c r="B281" t="inlineStr">
         <is>
           <t>International Test of English Proficiency, iTEP International, iTEP Slate</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Assessment / Exam competitor</t>
         </is>
       </c>
     </row>
